--- a/B2_seg推論統計_11m.xlsx
+++ b/B2_seg推論統計_11m.xlsx
@@ -2636,7 +2636,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>067_d0_jpg.rf.d69e1bebfb7e4f8d986ef8037968ad4d.jpg</t>
+          <t>067_d0_jpg.rf.ac90bce7f88c1b868e5f95777451272a.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2657,7 +2657,7 @@
         <v>415</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2985</v>
+        <v>0.995</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
